--- a/advertising_forms/009_magazine_model_release_form--advertising_forms.xlsx
+++ b/advertising_forms/009_magazine_model_release_form--advertising_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Client Name</t>
+          <t>Client Name Label</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Photographer Name</t>
+          <t>Photographer Name Label</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>photographer_agreement</t>
+          <t>photographer_agreement_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Photographer Agreement</t>
+          <t>Photographer Agreement 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Model Agreement</t>
+          <t>Model Agreement Label</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Signed By</t>
+          <t>Signed By Label</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
